--- a/Ciclo 01/RHU/Unidad 2/Planilla.Total.RHU115.25 -HT.xlsx
+++ b/Ciclo 01/RHU/Unidad 2/Planilla.Total.RHU115.25 -HT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INVERSIONES ALVEZ\Desktop\UES\2025\Ciclo I\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\RHU\Unidad 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1126E17F-804B-40AC-9AD4-785DA0748EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB05B58-855C-46D5-BED4-1C2FD678D76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="4" r:id="rId1"/>
@@ -21,40 +21,51 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Boleta de pago'!$1:$10</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="4">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="3"/>
         </ext>
       </extLst>
@@ -251,9 +262,6 @@
     <t>Horas extras nocturnas (hrs /mes)</t>
   </si>
   <si>
-    <t>El monto total de las horas extras dirunas, nocturnas</t>
-  </si>
-  <si>
     <t>El monto total de la nocturnidad</t>
   </si>
   <si>
@@ -499,6 +507,9 @@
   </si>
   <si>
     <t>Contabilidad</t>
+  </si>
+  <si>
+    <t>El monto total de las horas extras diunas, nocturnas</t>
   </si>
 </sst>
 </file>
@@ -506,10 +517,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;CV&quot;0000"/>
-    <numFmt numFmtId="166" formatCode="00000000000000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="&quot;CV&quot;0000"/>
+    <numFmt numFmtId="167" formatCode="00000000000000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -990,11 +1001,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1023,19 +1034,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1059,13 +1070,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1086,7 +1097,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1104,19 +1115,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1131,10 +1139,10 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1143,16 +1151,13 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1161,16 +1166,13 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1184,21 +1186,24 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1343,8 +1348,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1354,42 +1392,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1699,18 +1701,17 @@
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
 <rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <rv s="0">
-    <v>0</v>
-    <v>5</v>
+    <v>11</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <v>1</v>
     <v>5</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <v>2</v>
     <v>5</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>3</v>
     <v>5</v>
     <v>Apple con relleno sólido</v>
@@ -1719,7 +1720,10 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+  </s>
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
     <k n="CalcOrigin" t="i"/>
@@ -2029,113 +2033,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:L19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="8"/>
+    <col min="1" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="76" t="e" vm="1">
+    <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="74" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="78"/>
-      <c r="J3" s="76" t="e" vm="2">
+      <c r="C3" s="75"/>
+      <c r="D3" s="76"/>
+      <c r="J3" s="74" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="K3" s="77"/>
-      <c r="L3" s="78"/>
-    </row>
-    <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="81"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="81"/>
-    </row>
-    <row r="5" spans="2:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="81"/>
-      <c r="F5" s="85" t="s">
+      <c r="K3" s="75"/>
+      <c r="L3" s="76"/>
+    </row>
+    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="77"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="79"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="79"/>
+    </row>
+    <row r="5" spans="2:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="77"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="79"/>
+      <c r="F5" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="86"/>
-      <c r="H5" s="87"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="81"/>
-    </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="81"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="90"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="81"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="81"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="81"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="81"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="81"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="79"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="81"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="80"/>
-      <c r="L9" s="81"/>
-    </row>
-    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="79"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="81"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="81"/>
-    </row>
-    <row r="11" spans="2:12" ht="58.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="79"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81"/>
-      <c r="F11" s="91" t="s">
+      <c r="G5" s="84"/>
+      <c r="H5" s="85"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="79"/>
+    </row>
+    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="77"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="79"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="88"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="79"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="77"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="79"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="79"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="77"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="79"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="79"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="79"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="79"/>
+    </row>
+    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="79"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="79"/>
+    </row>
+    <row r="11" spans="2:12" ht="58.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="77"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="79"/>
+      <c r="F11" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="92"/>
-      <c r="H11" s="93"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="82"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="84"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="84"/>
-    </row>
-    <row r="14" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="91"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="79"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="80"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="82"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="82"/>
+    </row>
+    <row r="14" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:D12"/>
@@ -2151,112 +2155,112 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="3" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="22" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="1"/>
+    <col min="7" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="e" vm="3">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="104" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="112" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="97" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="98"/>
-      <c r="I1" s="99"/>
-    </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="103" t="s">
+      <c r="H1" s="96"/>
+      <c r="I1" s="97"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="106"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="104"/>
-      <c r="I2" s="105"/>
-    </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="100" t="s">
+      <c r="H2" s="102"/>
+      <c r="I2" s="103"/>
+    </row>
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="108"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="99"/>
+      <c r="I3" s="100"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="121" t="s">
+      <c r="C5" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="121" t="s">
+      <c r="C6" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-    </row>
-    <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+    </row>
+    <row r="7" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="121" t="s">
+      <c r="C7" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
@@ -2271,202 +2275,202 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="122" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-    </row>
-    <row r="12" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="123" t="s">
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+    </row>
+    <row r="12" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="123"/>
-    </row>
-    <row r="14" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="121"/>
+      <c r="I12" s="121"/>
+    </row>
+    <row r="14" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C14" s="94" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="96"/>
-    </row>
-    <row r="16" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="92" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="94"/>
+    </row>
+    <row r="16" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C16" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="96"/>
-    </row>
-    <row r="18" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="94"/>
+    </row>
+    <row r="18" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C18" s="94" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="96"/>
-    </row>
-    <row r="20" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="94"/>
+    </row>
+    <row r="20" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C20" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="96"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C20" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="94"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C22" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="95"/>
-      <c r="I22" s="96"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C22" s="92" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="94"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C24" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="96"/>
-    </row>
-    <row r="26" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="94"/>
+    </row>
+    <row r="26" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C26" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
-      <c r="I26" s="96"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C26" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="94"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C28" s="94" t="s">
+      <c r="C28" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="95"/>
-      <c r="H28" s="95"/>
-      <c r="I28" s="96"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D28" s="93"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="94"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C30" s="94" t="s">
+      <c r="C30" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="96"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="94"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="95"/>
-      <c r="E32" s="95"/>
-      <c r="F32" s="95"/>
-      <c r="G32" s="95"/>
-      <c r="H32" s="95"/>
-      <c r="I32" s="96"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="94"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C34" s="94" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="95"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="95"/>
-      <c r="G34" s="95"/>
-      <c r="H34" s="95"/>
-      <c r="I34" s="96"/>
-    </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C34" s="92" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="93"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="C36" s="94" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="95"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
-      <c r="I36" s="96"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D39" s="66" t="s">
+      <c r="C36" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="94"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D39" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E39" s="66" t="s">
+      <c r="E39" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="F39" s="67"/>
-    </row>
-    <row r="41" spans="2:14" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="F39" s="64"/>
+    </row>
+    <row r="41" spans="2:14" ht="69" x14ac:dyDescent="0.3">
       <c r="C41" s="21" t="s">
         <v>10</v>
       </c>
@@ -2474,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41" s="21" t="s">
         <v>1</v>
@@ -2500,11 +2504,11 @@
       <c r="M41" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N41" s="51" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N41" s="50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C42" s="23">
         <v>1</v>
       </c>
@@ -2512,7 +2516,7 @@
         <v>7</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F42" s="25" t="s">
         <v>20</v>
@@ -2539,11 +2543,11 @@
       <c r="M42" s="23">
         <v>0</v>
       </c>
-      <c r="N42" s="52">
+      <c r="N42" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C43" s="23">
         <f>1+C42</f>
         <v>2</v>
@@ -2552,7 +2556,7 @@
         <v>11</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" s="25" t="s">
         <v>12</v>
@@ -2579,11 +2583,11 @@
       <c r="M43" s="23">
         <v>0</v>
       </c>
-      <c r="N43" s="52">
+      <c r="N43" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C44" s="23">
         <f t="shared" ref="C44:C45" si="1">1+C43</f>
         <v>3</v>
@@ -2592,7 +2596,7 @@
         <v>13</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F44" s="25" t="s">
         <v>5</v>
@@ -2620,11 +2624,11 @@
       <c r="M44" s="23">
         <v>0</v>
       </c>
-      <c r="N44" s="52">
+      <c r="N44" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C45" s="23">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -2632,8 +2636,8 @@
       <c r="D45" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="60" t="s">
-        <v>102</v>
+      <c r="E45" s="58" t="s">
+        <v>101</v>
       </c>
       <c r="F45" s="32" t="s">
         <v>15</v>
@@ -2661,11 +2665,11 @@
       <c r="M45" s="23">
         <v>0</v>
       </c>
-      <c r="N45" s="52">
+      <c r="N45" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C46" s="23"/>
       <c r="D46" s="24"/>
       <c r="E46" s="32"/>
@@ -2682,9 +2686,9 @@
       <c r="K46" s="42"/>
       <c r="L46" s="42"/>
       <c r="M46" s="42"/>
-      <c r="N46" s="53"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N46" s="52"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C47" s="23">
         <f>+C45+1</f>
         <v>5</v>
@@ -2693,7 +2697,7 @@
         <v>16</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" s="32" t="s">
         <v>17</v>
@@ -2722,11 +2726,11 @@
         <f>39*2</f>
         <v>78</v>
       </c>
-      <c r="N47" s="52">
+      <c r="N47" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C48" s="23">
         <f>+C47+1</f>
         <v>6</v>
@@ -2735,10 +2739,10 @@
         <v>16</v>
       </c>
       <c r="E48" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F48" s="32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G48" s="33">
         <v>41883</v>
@@ -2763,11 +2767,11 @@
       <c r="M48" s="23">
         <v>14</v>
       </c>
-      <c r="N48" s="52">
+      <c r="N48" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C49" s="23">
         <f t="shared" ref="C49:C53" si="3">+C48+1</f>
         <v>7</v>
@@ -2776,10 +2780,10 @@
         <v>16</v>
       </c>
       <c r="E49" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G49" s="33">
         <v>44197</v>
@@ -2804,11 +2808,11 @@
       <c r="M49" s="23">
         <v>78</v>
       </c>
-      <c r="N49" s="52">
+      <c r="N49" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="23">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -2817,10 +2821,10 @@
         <v>16</v>
       </c>
       <c r="E50" s="32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F50" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G50" s="33">
         <v>44896</v>
@@ -2845,11 +2849,11 @@
       <c r="M50" s="23">
         <v>39</v>
       </c>
-      <c r="N50" s="52">
+      <c r="N50" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C51" s="23">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -2858,10 +2862,10 @@
         <v>16</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G51" s="33">
         <v>43815</v>
@@ -2886,11 +2890,11 @@
       <c r="M51" s="23">
         <v>39</v>
       </c>
-      <c r="N51" s="52">
+      <c r="N51" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C52" s="23">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -2899,7 +2903,7 @@
         <v>16</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F52" s="32" t="s">
         <v>18</v>
@@ -2928,11 +2932,11 @@
         <f>39*4</f>
         <v>156</v>
       </c>
-      <c r="N52" s="52">
+      <c r="N52" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="23">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -2941,7 +2945,7 @@
         <v>16</v>
       </c>
       <c r="E53" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F53" s="32" t="s">
         <v>19</v>
@@ -2969,57 +2973,50 @@
       <c r="M53" s="23">
         <v>0</v>
       </c>
-      <c r="N53" s="52">
+      <c r="N53" s="51">
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C54" s="67"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="69"/>
-      <c r="H54" s="69"/>
-      <c r="I54" s="70" t="s">
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C54" s="64"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="J54" s="71">
+      <c r="J54" s="68">
         <f t="shared" ref="J54" si="6">SUM(J47:J53)</f>
         <v>3130</v>
       </c>
-      <c r="K54" s="71"/>
-      <c r="L54" s="71"/>
-      <c r="M54" s="71"/>
-      <c r="N54" s="71"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="69"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="70" t="s">
+      <c r="K54" s="68"/>
+      <c r="L54" s="68"/>
+      <c r="M54" s="68"/>
+      <c r="N54" s="68"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C55" s="64"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="64"/>
+      <c r="I55" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="J55" s="72">
+      <c r="J55" s="69">
         <f>+J46+J54</f>
         <v>6680</v>
       </c>
-      <c r="K55" s="72"/>
-      <c r="L55" s="72"/>
-      <c r="M55" s="72"/>
-      <c r="N55" s="72"/>
+      <c r="K55" s="69"/>
+      <c r="L55" s="69"/>
+      <c r="M55" s="69"/>
+      <c r="N55" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="C32:I32"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C18:I18"/>
     <mergeCell ref="C20:I20"/>
@@ -3035,6 +3032,13 @@
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="C12:I12"/>
     <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C32:I32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3043,29 +3047,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AD43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="8" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="8" customWidth="1"/>
-    <col min="8" max="11" width="11.42578125" style="8"/>
-    <col min="12" max="18" width="12.7109375" style="8" customWidth="1"/>
-    <col min="19" max="19" width="12.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="8" customWidth="1"/>
-    <col min="21" max="22" width="12.5703125" style="8" customWidth="1"/>
-    <col min="23" max="23" width="12.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.28515625" style="8" customWidth="1"/>
-    <col min="25" max="25" width="11.5703125" style="8" customWidth="1"/>
-    <col min="26" max="26" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="11.42578125" style="8"/>
+    <col min="3" max="3" width="7.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="8" customWidth="1"/>
+    <col min="8" max="11" width="11.44140625" style="8"/>
+    <col min="12" max="18" width="12.6640625" style="8" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.6640625" style="8" customWidth="1"/>
+    <col min="21" max="22" width="12.5546875" style="8" customWidth="1"/>
+    <col min="23" max="23" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.33203125" style="8" customWidth="1"/>
+    <col min="25" max="25" width="11.5546875" style="8" customWidth="1"/>
+    <col min="26" max="26" width="10.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="50">
+    <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="49">
         <v>45657</v>
       </c>
       <c r="F1" s="14">
@@ -3073,17 +3077,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="E3" s="66" t="s">
+    <row r="2" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="E3" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="67"/>
-    </row>
-    <row r="4" spans="1:30" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="64"/>
+    </row>
+    <row r="4" spans="1:30" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="U4" s="10">
         <v>7.4999999999999997E-2</v>
       </c>
@@ -3102,40 +3106,40 @@
       <c r="Z4" s="10">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="AD4" s="49" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="124" t="s">
+      <c r="AD4" s="48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="124"/>
-      <c r="R5" s="124"/>
-      <c r="S5" s="124"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="124"/>
-      <c r="W5" s="124"/>
-      <c r="X5" s="124"/>
-      <c r="Y5" s="124"/>
-      <c r="Z5" s="124"/>
-    </row>
-    <row r="6" spans="1:30" ht="51" x14ac:dyDescent="0.25">
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="73"/>
+      <c r="U5" s="73"/>
+      <c r="V5" s="73"/>
+      <c r="W5" s="73"/>
+      <c r="X5" s="73"/>
+      <c r="Y5" s="73"/>
+      <c r="Z5" s="73"/>
+    </row>
+    <row r="6" spans="1:30" ht="69" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
         <v>10</v>
       </c>
@@ -3143,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>1</v>
@@ -3169,56 +3173,56 @@
       <c r="K6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="51" t="s">
-        <v>47</v>
+      <c r="L6" s="50" t="s">
+        <v>46</v>
       </c>
       <c r="M6" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="R6" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="T6" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="U6" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="O6" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="P6" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q6" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="R6" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" s="21" t="s">
+      <c r="V6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="T6" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="U6" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="V6" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="W6" s="22" t="s">
+      <c r="X6" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="X6" s="22" t="s">
+      <c r="Y6" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="Y6" s="54" t="s">
+      <c r="Z6" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="Z6" s="55" t="s">
-        <v>62</v>
-      </c>
       <c r="AD6" s="22" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="23">
         <v>1</v>
       </c>
@@ -3226,7 +3230,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" s="25" t="s">
         <v>20</v>
@@ -3253,35 +3257,71 @@
       <c r="K7" s="23">
         <v>0</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7" s="51">
         <v>30</v>
       </c>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="62"/>
+      <c r="M7" s="43">
+        <f>H7/30/8*I7*2</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="43">
+        <f>(H7/30/8)*J7*2.5</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="43">
+        <f>(H7/30/8)*K7*0.25</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="30">
+        <f>+(H7/2)*0.3</f>
+        <v>225</v>
+      </c>
+      <c r="Q7" s="60">
+        <f>IF(G7&lt;1,H7/30*15*G7,IF(G7&lt;3,H7/30*15,IF(G7&lt;10,H7/30*19,H7/30*21)))</f>
+        <v>1050</v>
+      </c>
       <c r="R7" s="30">
         <f>+Q7-S7</f>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="S7" s="30">
-        <f>IF(Q7&gt;=1200,(Q7-1200),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T7" s="44"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="56"/>
-      <c r="Z7" s="56"/>
+        <f>IF(Q7&gt;=1500,(Q7-1500),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="44">
+        <f>H7+M7+N7+O7+P7</f>
+        <v>1725</v>
+      </c>
+      <c r="U7" s="29">
+        <f>IF(T7&gt;1000,1000*7.5%,T7*7.5%)</f>
+        <v>75</v>
+      </c>
+      <c r="V7" s="29">
+        <f>IF(T7&gt;1000,1000*3%,T7*3%)</f>
+        <v>30</v>
+      </c>
+      <c r="W7" s="29">
+        <f>+T7*8.75%</f>
+        <v>150.9375</v>
+      </c>
+      <c r="X7" s="29">
+        <f>+T7*7.25%</f>
+        <v>125.06249999999999</v>
+      </c>
+      <c r="Y7" s="55">
+        <f>+Q7+T7-V7-X7</f>
+        <v>2619.9375</v>
+      </c>
+      <c r="Z7" s="55">
+        <f>+U7+V7+W7+X7</f>
+        <v>381</v>
+      </c>
       <c r="AD7" s="43">
         <f t="shared" ref="AD7:AD20" si="0">+M7+N7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="23">
         <f>1+A7</f>
         <v>2</v>
@@ -3290,7 +3330,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" s="25" t="s">
         <v>12</v>
@@ -3317,44 +3357,80 @@
       <c r="K8" s="23">
         <v>0</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8" s="51">
         <v>30</v>
       </c>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="62"/>
+      <c r="M8" s="43">
+        <f t="shared" ref="M8:M18" si="2">H8/30/8*I8*2</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="43">
+        <f t="shared" ref="N8:N18" si="3">(H8/30/8)*J8*2.5</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="43">
+        <f t="shared" ref="O8:O18" si="4">(H8/30/8)*K8*0.25</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="30">
+        <f t="shared" ref="P8:P10" si="5">+(H8/2)*0.3</f>
+        <v>67.5</v>
+      </c>
+      <c r="Q8" s="60">
+        <f>IF(G8&lt;1,H8/30*15*G8,IF(G8&lt;3,H8/30*15,IF(G8&lt;10,H8/30*19,H8/30*21)))</f>
+        <v>315</v>
+      </c>
       <c r="R8" s="30">
-        <f t="shared" ref="R8:R18" si="2">+Q8-S8</f>
-        <v>0</v>
+        <f t="shared" ref="R8:R18" si="6">+Q8-S8</f>
+        <v>315</v>
       </c>
       <c r="S8" s="30">
-        <f t="shared" ref="S8:S10" si="3">IF(Q8&gt;=1200,(1200-Q8),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T8" s="44"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
+        <f t="shared" ref="S8:S18" si="7">IF(Q8&gt;=1500,(Q8-1500),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="44">
+        <f t="shared" ref="T8:T18" si="8">H8+M8+N8+O8+P8</f>
+        <v>517.5</v>
+      </c>
+      <c r="U8" s="29">
+        <f t="shared" ref="U8:U18" si="9">IF(T8&gt;1000,1000*7.5%,T8*7.5%)</f>
+        <v>38.8125</v>
+      </c>
+      <c r="V8" s="29">
+        <f t="shared" ref="V8:V18" si="10">IF(T8&gt;1000,1000*3%,T8*3%)</f>
+        <v>15.524999999999999</v>
+      </c>
+      <c r="W8" s="29">
+        <f t="shared" ref="W8:W18" si="11">+T8*8.75%</f>
+        <v>45.28125</v>
+      </c>
+      <c r="X8" s="29">
+        <f t="shared" ref="X8:X18" si="12">+T8*7.25%</f>
+        <v>37.518749999999997</v>
+      </c>
+      <c r="Y8" s="55">
+        <f t="shared" ref="Y8:Y18" si="13">+Q8+T8-V8-X8</f>
+        <v>779.45625000000007</v>
+      </c>
+      <c r="Z8" s="55">
+        <f t="shared" ref="Z8:Z18" si="14">+U8+V8+W8+X8</f>
+        <v>137.13749999999999</v>
+      </c>
       <c r="AD8" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="23">
-        <f t="shared" ref="A9:A10" si="4">1+A8</f>
+        <f t="shared" ref="A9:A10" si="15">1+A8</f>
         <v>3</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" s="25" t="s">
         <v>5</v>
@@ -3381,44 +3457,80 @@
       <c r="K9" s="23">
         <v>0</v>
       </c>
-      <c r="L9" s="52">
+      <c r="L9" s="51">
         <v>30</v>
       </c>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="62"/>
+      <c r="M9" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="30">
+        <f t="shared" si="5"/>
+        <v>135</v>
+      </c>
+      <c r="Q9" s="60">
+        <f>IF(G9&lt;1,H9/30*15*G9,IF(G9&lt;3,H9/30*15,IF(G9&lt;10,H9/30*19,H9/30*21)))</f>
+        <v>570</v>
+      </c>
       <c r="R9" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>570</v>
       </c>
       <c r="S9" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T9" s="44"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="56"/>
-      <c r="Z9" s="56"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="44">
+        <f t="shared" si="8"/>
+        <v>1035</v>
+      </c>
+      <c r="U9" s="29">
+        <f t="shared" si="9"/>
+        <v>75</v>
+      </c>
+      <c r="V9" s="29">
+        <f t="shared" si="10"/>
+        <v>30</v>
+      </c>
+      <c r="W9" s="29">
+        <f t="shared" si="11"/>
+        <v>90.5625</v>
+      </c>
+      <c r="X9" s="29">
+        <f t="shared" si="12"/>
+        <v>75.037499999999994</v>
+      </c>
+      <c r="Y9" s="55">
+        <f t="shared" si="13"/>
+        <v>1499.9625000000001</v>
+      </c>
+      <c r="Z9" s="55">
+        <f t="shared" si="14"/>
+        <v>270.60000000000002</v>
+      </c>
       <c r="AD9" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>102</v>
+        <v>125</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>101</v>
       </c>
       <c r="D10" s="32" t="s">
         <v>15</v>
@@ -3445,35 +3557,71 @@
       <c r="K10" s="23">
         <v>0</v>
       </c>
-      <c r="L10" s="52">
+      <c r="L10" s="51">
         <v>30</v>
       </c>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="62"/>
+      <c r="M10" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="30">
+        <f t="shared" si="5"/>
+        <v>165</v>
+      </c>
+      <c r="Q10" s="60">
+        <f>IF(G10&lt;1,H10/30*15*G10,IF(G10&lt;3,H10/30*15,IF(G10&lt;10,H10/30*19,H10/30*21)))</f>
+        <v>696.66666666666663</v>
+      </c>
       <c r="R10" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>696.66666666666663</v>
       </c>
       <c r="S10" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="44"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="56"/>
-      <c r="Z10" s="56"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="44">
+        <f t="shared" si="8"/>
+        <v>1265</v>
+      </c>
+      <c r="U10" s="29">
+        <f t="shared" si="9"/>
+        <v>75</v>
+      </c>
+      <c r="V10" s="29">
+        <f t="shared" si="10"/>
+        <v>30</v>
+      </c>
+      <c r="W10" s="29">
+        <f t="shared" si="11"/>
+        <v>110.6875</v>
+      </c>
+      <c r="X10" s="29">
+        <f t="shared" si="12"/>
+        <v>91.712499999999991</v>
+      </c>
+      <c r="Y10" s="55">
+        <f t="shared" si="13"/>
+        <v>1839.9541666666664</v>
+      </c>
+      <c r="Z10" s="55">
+        <f t="shared" si="14"/>
+        <v>307.39999999999998</v>
+      </c>
       <c r="AD10" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
       <c r="B11" s="24"/>
       <c r="C11" s="32"/>
@@ -3490,69 +3638,69 @@
       <c r="I11" s="42"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
-      <c r="L11" s="53"/>
+      <c r="L11" s="52"/>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:O11" si="5">SUM(M7:M10)</f>
+        <f>SUM(M7:M10)</f>
         <v>0</v>
       </c>
       <c r="N11" s="37">
-        <f t="shared" si="5"/>
+        <f>SUM(N7:N10)</f>
         <v>0</v>
       </c>
       <c r="O11" s="37">
-        <f t="shared" si="5"/>
+        <f>SUM(O7:O10)</f>
         <v>0</v>
       </c>
       <c r="P11" s="37">
         <f>SUM(P7:P10)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="63">
+        <v>592.5</v>
+      </c>
+      <c r="Q11" s="37">
         <f>SUM(Q7:Q10)</f>
-        <v>0</v>
+        <v>2631.6666666666665</v>
       </c>
       <c r="R11" s="37">
         <f>SUM(R7:R10)</f>
-        <v>0</v>
+        <v>2631.6666666666665</v>
       </c>
       <c r="S11" s="37">
         <f>SUM(S7:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="45">
+      <c r="T11" s="37">
         <f>SUM(T7:T10)</f>
-        <v>0</v>
+        <v>4542.5</v>
       </c>
       <c r="U11" s="37">
-        <f t="shared" ref="U11:Y11" si="6">SUM(U7:U10)</f>
-        <v>0</v>
+        <f>SUM(U7:U10)</f>
+        <v>263.8125</v>
       </c>
       <c r="V11" s="37">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>SUM(V7:V10)</f>
+        <v>105.52500000000001</v>
       </c>
       <c r="W11" s="37">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>SUM(W7:W10)</f>
+        <v>397.46875</v>
       </c>
       <c r="X11" s="37">
-        <f t="shared" ref="X11" si="7">SUM(X7:X10)</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="57">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="57">
+        <f>SUM(X7:X10)</f>
+        <v>329.33124999999995</v>
+      </c>
+      <c r="Y11" s="37">
+        <f>SUM(Y7:Y10)</f>
+        <v>6739.3104166666672</v>
+      </c>
+      <c r="Z11" s="37">
         <f>SUM(Z7:Z10)</f>
-        <v>0</v>
+        <v>1096.1375</v>
       </c>
       <c r="AD11" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="23">
         <f>+A10+1</f>
         <v>5</v>
@@ -3561,7 +3709,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>17</v>
@@ -3590,38 +3738,71 @@
         <f>39*2</f>
         <v>78</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12" s="51">
         <v>30</v>
       </c>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="62"/>
+      <c r="M12" s="43">
+        <f t="shared" si="2"/>
+        <v>243.75</v>
+      </c>
+      <c r="N12" s="43">
+        <f>(H12/30/8)*J12*2.5</f>
+        <v>169.27083333333337</v>
+      </c>
+      <c r="O12" s="43">
+        <f t="shared" si="4"/>
+        <v>52.8125</v>
+      </c>
+      <c r="P12" s="30">
+        <f>+(H12/2)*0.3</f>
+        <v>97.5</v>
+      </c>
+      <c r="Q12" s="60">
+        <f t="shared" ref="Q11:Q18" si="16">IF(G12&lt;1,H12/30*15*G12,IF(G12&lt;3,H12/30*15,IF(G12&lt;10,H12/30*19,H12/30*21)))</f>
+        <v>411.66666666666669</v>
+      </c>
       <c r="R12" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>411.66666666666669</v>
       </c>
       <c r="S12" s="30">
-        <f t="shared" ref="S12:S18" si="8">IF(Q12&gt;=1200,(1200-Q12),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T12" s="44"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="56"/>
-      <c r="Z12" s="56">
-        <f t="shared" ref="Z12:Z18" si="9">+U12+V12+W12+X12</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="44">
+        <f t="shared" si="8"/>
+        <v>1213.3333333333335</v>
+      </c>
+      <c r="U12" s="29">
+        <f t="shared" si="9"/>
+        <v>75</v>
+      </c>
+      <c r="V12" s="29">
+        <f t="shared" si="10"/>
+        <v>30</v>
+      </c>
+      <c r="W12" s="29">
+        <f t="shared" si="11"/>
+        <v>106.16666666666667</v>
+      </c>
+      <c r="X12" s="29">
+        <f t="shared" si="12"/>
+        <v>87.966666666666669</v>
+      </c>
+      <c r="Y12" s="55">
+        <f t="shared" si="13"/>
+        <v>1507.0333333333335</v>
+      </c>
+      <c r="Z12" s="55">
+        <f t="shared" si="14"/>
+        <v>299.13333333333333</v>
       </c>
       <c r="AD12" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+        <v>413.02083333333337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="23">
         <f>+A12+1</f>
         <v>6</v>
@@ -3630,10 +3811,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="33">
         <v>41883</v>
@@ -3653,61 +3834,94 @@
         <v>65</v>
       </c>
       <c r="J13" s="23">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K13" s="23">
         <v>14</v>
       </c>
-      <c r="L13" s="52">
+      <c r="L13" s="51">
         <v>30</v>
       </c>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="62"/>
+      <c r="M13" s="43">
+        <f t="shared" si="2"/>
+        <v>235.625</v>
+      </c>
+      <c r="N13" s="43">
+        <f t="shared" si="3"/>
+        <v>95.15625</v>
+      </c>
+      <c r="O13" s="43">
+        <f t="shared" si="4"/>
+        <v>6.34375</v>
+      </c>
+      <c r="P13" s="30">
+        <f t="shared" ref="P13:P18" si="17">+(H13/2)*0.3</f>
+        <v>65.25</v>
+      </c>
+      <c r="Q13" s="60">
+        <f t="shared" si="16"/>
+        <v>304.5</v>
+      </c>
       <c r="R13" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>304.5</v>
       </c>
       <c r="S13" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="44"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="56"/>
-      <c r="Z13" s="56">
+        <v>837.375</v>
+      </c>
+      <c r="U13" s="29">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>62.803124999999994</v>
+      </c>
+      <c r="V13" s="29">
+        <f t="shared" si="10"/>
+        <v>25.12125</v>
+      </c>
+      <c r="W13" s="29">
+        <f t="shared" si="11"/>
+        <v>73.270312499999989</v>
+      </c>
+      <c r="X13" s="29">
+        <f t="shared" si="12"/>
+        <v>60.709687499999994</v>
+      </c>
+      <c r="Y13" s="55">
+        <f t="shared" si="13"/>
+        <v>1056.0440625000001</v>
+      </c>
+      <c r="Z13" s="55">
+        <f t="shared" si="14"/>
+        <v>221.90437499999999</v>
       </c>
       <c r="AD13" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+        <v>330.78125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="23">
-        <f t="shared" ref="A14:A17" si="10">+A13+1</f>
+        <f t="shared" ref="A14:A17" si="18">+A13+1</f>
         <v>7</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E14" s="33">
         <v>44197</v>
       </c>
       <c r="F14" s="33">
-        <f t="shared" ref="F14:F16" si="11">+F13</f>
+        <f t="shared" ref="F14:F16" si="19">+F13</f>
         <v>46022</v>
       </c>
       <c r="G14" s="27">
@@ -3726,56 +3940,89 @@
       <c r="K14" s="23">
         <v>78</v>
       </c>
-      <c r="L14" s="52">
+      <c r="L14" s="51">
         <v>30</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="62"/>
+      <c r="M14" s="43">
+        <f t="shared" si="2"/>
+        <v>113.75</v>
+      </c>
+      <c r="N14" s="43">
+        <f t="shared" si="3"/>
+        <v>101.5625</v>
+      </c>
+      <c r="O14" s="43">
+        <f t="shared" si="4"/>
+        <v>31.6875</v>
+      </c>
+      <c r="P14" s="30">
+        <f t="shared" si="17"/>
+        <v>58.5</v>
+      </c>
+      <c r="Q14" s="60">
+        <f t="shared" si="16"/>
+        <v>247</v>
+      </c>
       <c r="R14" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>247</v>
       </c>
       <c r="S14" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="44"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="56"/>
-      <c r="Z14" s="56">
+        <v>695.5</v>
+      </c>
+      <c r="U14" s="29">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>52.162500000000001</v>
+      </c>
+      <c r="V14" s="29">
+        <f t="shared" si="10"/>
+        <v>20.864999999999998</v>
+      </c>
+      <c r="W14" s="29">
+        <f t="shared" si="11"/>
+        <v>60.856249999999996</v>
+      </c>
+      <c r="X14" s="29">
+        <f t="shared" si="12"/>
+        <v>50.423749999999998</v>
+      </c>
+      <c r="Y14" s="55">
+        <f t="shared" si="13"/>
+        <v>871.21124999999995</v>
+      </c>
+      <c r="Z14" s="55">
+        <f t="shared" si="14"/>
+        <v>184.3075</v>
       </c>
       <c r="AD14" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+        <v>215.3125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>8</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E15" s="33">
         <v>44896</v>
       </c>
       <c r="F15" s="33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>46022</v>
       </c>
       <c r="G15" s="27">
@@ -3794,56 +4041,89 @@
       <c r="K15" s="23">
         <v>39</v>
       </c>
-      <c r="L15" s="52">
+      <c r="L15" s="51">
         <v>30</v>
       </c>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="62"/>
+      <c r="M15" s="43">
+        <f t="shared" si="2"/>
+        <v>76.041666666666657</v>
+      </c>
+      <c r="N15" s="43">
+        <f t="shared" si="3"/>
+        <v>133.07291666666666</v>
+      </c>
+      <c r="O15" s="43">
+        <f t="shared" si="4"/>
+        <v>14.828125</v>
+      </c>
+      <c r="P15" s="30">
+        <f t="shared" si="17"/>
+        <v>54.75</v>
+      </c>
+      <c r="Q15" s="60">
+        <f t="shared" si="16"/>
+        <v>231.16666666666666</v>
+      </c>
       <c r="R15" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>231.16666666666666</v>
       </c>
       <c r="S15" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="44"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="56"/>
-      <c r="Z15" s="56">
+        <v>643.69270833333326</v>
+      </c>
+      <c r="U15" s="29">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48.276953124999991</v>
+      </c>
+      <c r="V15" s="29">
+        <f t="shared" si="10"/>
+        <v>19.310781249999998</v>
+      </c>
+      <c r="W15" s="29">
+        <f t="shared" si="11"/>
+        <v>56.323111979166654</v>
+      </c>
+      <c r="X15" s="29">
+        <f t="shared" si="12"/>
+        <v>46.667721354166659</v>
+      </c>
+      <c r="Y15" s="55">
+        <f t="shared" si="13"/>
+        <v>808.88087239583319</v>
+      </c>
+      <c r="Z15" s="55">
+        <f t="shared" si="14"/>
+        <v>170.57856770833331</v>
       </c>
       <c r="AD15" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+        <v>209.11458333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E16" s="33">
         <v>43815</v>
       </c>
       <c r="F16" s="33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>46022</v>
       </c>
       <c r="G16" s="27">
@@ -3862,47 +4142,80 @@
       <c r="K16" s="23">
         <v>39</v>
       </c>
-      <c r="L16" s="52">
+      <c r="L16" s="51">
         <v>30</v>
       </c>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="62"/>
+      <c r="M16" s="43">
+        <f t="shared" si="2"/>
+        <v>41.5</v>
+      </c>
+      <c r="N16" s="43">
+        <f t="shared" si="3"/>
+        <v>86.458333333333343</v>
+      </c>
+      <c r="O16" s="43">
+        <f t="shared" si="4"/>
+        <v>16.859375</v>
+      </c>
+      <c r="P16" s="30">
+        <f t="shared" si="17"/>
+        <v>62.25</v>
+      </c>
+      <c r="Q16" s="60">
+        <f t="shared" si="16"/>
+        <v>262.83333333333337</v>
+      </c>
       <c r="R16" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>262.83333333333337</v>
       </c>
       <c r="S16" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="44"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="56"/>
-      <c r="Z16" s="56">
+        <v>622.06770833333337</v>
+      </c>
+      <c r="U16" s="29">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>46.655078125000003</v>
+      </c>
+      <c r="V16" s="29">
+        <f t="shared" si="10"/>
+        <v>18.662031250000002</v>
+      </c>
+      <c r="W16" s="29">
+        <f t="shared" si="11"/>
+        <v>54.43092447916667</v>
+      </c>
+      <c r="X16" s="29">
+        <f t="shared" si="12"/>
+        <v>45.099908854166664</v>
+      </c>
+      <c r="Y16" s="55">
+        <f t="shared" si="13"/>
+        <v>821.13910156250006</v>
+      </c>
+      <c r="Z16" s="55">
+        <f t="shared" si="14"/>
+        <v>164.84794270833333</v>
       </c>
       <c r="AD16" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+        <v>127.95833333333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>10</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D17" s="32" t="s">
         <v>18</v>
@@ -3911,7 +4224,7 @@
         <v>43435</v>
       </c>
       <c r="F17" s="38">
-        <f t="shared" ref="F17:F18" si="12">+F12</f>
+        <f t="shared" ref="F17:F18" si="20">+F12</f>
         <v>46022</v>
       </c>
       <c r="G17" s="27">
@@ -3931,47 +4244,80 @@
         <f>39*4</f>
         <v>156</v>
       </c>
-      <c r="L17" s="52">
+      <c r="L17" s="51">
         <v>30</v>
       </c>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="62"/>
+      <c r="M17" s="43">
+        <f t="shared" si="2"/>
+        <v>71.25</v>
+      </c>
+      <c r="N17" s="43">
+        <f t="shared" si="3"/>
+        <v>117.1875</v>
+      </c>
+      <c r="O17" s="43">
+        <f t="shared" si="4"/>
+        <v>73.125</v>
+      </c>
+      <c r="P17" s="30">
+        <f t="shared" si="17"/>
+        <v>67.5</v>
+      </c>
+      <c r="Q17" s="60">
+        <f t="shared" si="16"/>
+        <v>285</v>
+      </c>
       <c r="R17" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>285</v>
       </c>
       <c r="S17" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="44"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="56"/>
-      <c r="Z17" s="56">
+        <v>779.0625</v>
+      </c>
+      <c r="U17" s="29">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>58.4296875</v>
+      </c>
+      <c r="V17" s="29">
+        <f t="shared" si="10"/>
+        <v>23.371874999999999</v>
+      </c>
+      <c r="W17" s="29">
+        <f t="shared" si="11"/>
+        <v>68.16796875</v>
+      </c>
+      <c r="X17" s="29">
+        <f t="shared" si="12"/>
+        <v>56.482031249999999</v>
+      </c>
+      <c r="Y17" s="55">
+        <f t="shared" si="13"/>
+        <v>984.20859374999998</v>
+      </c>
+      <c r="Z17" s="55">
+        <f t="shared" si="14"/>
+        <v>206.45156249999999</v>
       </c>
       <c r="AD17" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+        <v>188.4375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="23">
-        <f t="shared" ref="A18" si="13">+A17+1</f>
+        <f t="shared" ref="A18" si="21">+A17+1</f>
         <v>11</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>19</v>
@@ -3980,7 +4326,7 @@
         <v>45170</v>
       </c>
       <c r="F18" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>46022</v>
       </c>
       <c r="G18" s="27">
@@ -3999,38 +4345,71 @@
       <c r="K18" s="23">
         <v>0</v>
       </c>
-      <c r="L18" s="52">
+      <c r="L18" s="51">
         <v>30</v>
       </c>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="62"/>
+      <c r="M18" s="43">
+        <f t="shared" si="2"/>
+        <v>155.83333333333331</v>
+      </c>
+      <c r="N18" s="43">
+        <f t="shared" si="3"/>
+        <v>146.09375</v>
+      </c>
+      <c r="O18" s="43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="30">
+        <f t="shared" si="17"/>
+        <v>63.75</v>
+      </c>
+      <c r="Q18" s="60">
+        <f t="shared" si="16"/>
+        <v>212.5</v>
+      </c>
       <c r="R18" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>212.5</v>
       </c>
       <c r="S18" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="44"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="56"/>
-      <c r="Z18" s="56">
+        <v>790.67708333333326</v>
+      </c>
+      <c r="U18" s="29">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>59.300781249999993</v>
+      </c>
+      <c r="V18" s="29">
+        <f t="shared" si="10"/>
+        <v>23.720312499999999</v>
+      </c>
+      <c r="W18" s="29">
+        <f t="shared" si="11"/>
+        <v>69.184244791666657</v>
+      </c>
+      <c r="X18" s="29">
+        <f t="shared" si="12"/>
+        <v>57.324088541666654</v>
+      </c>
+      <c r="Y18" s="55">
+        <f t="shared" si="13"/>
+        <v>922.13268229166658</v>
+      </c>
+      <c r="Z18" s="55">
+        <f t="shared" si="14"/>
+        <v>209.5294270833333</v>
       </c>
       <c r="AD18" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+        <v>301.92708333333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
@@ -4041,7 +4420,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="19">
-        <f t="shared" ref="H19:Z19" si="14">SUM(H12:H18)</f>
+        <f t="shared" ref="H19:Z19" si="22">SUM(H12:H18)</f>
         <v>3130</v>
       </c>
       <c r="I19" s="19"/>
@@ -4049,67 +4428,67 @@
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19">
-        <f t="shared" ref="M19:O19" si="15">SUM(M12:M18)</f>
-        <v>0</v>
+        <f t="shared" ref="M19:O19" si="23">SUM(M12:M18)</f>
+        <v>937.75</v>
       </c>
       <c r="N19" s="19">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>848.80208333333337</v>
       </c>
       <c r="O19" s="19">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>195.65625</v>
       </c>
       <c r="P19" s="19">
         <f>SUM(P12:P18)</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="64">
+        <v>469.5</v>
+      </c>
+      <c r="Q19" s="61">
         <f>SUM(Q12:Q18)</f>
-        <v>0</v>
+        <v>1954.666666666667</v>
       </c>
       <c r="R19" s="19">
         <f>SUM(R12:R18)</f>
-        <v>0</v>
+        <v>1954.666666666667</v>
       </c>
       <c r="S19" s="19">
         <f>SUM(S12:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="46">
+      <c r="T19" s="45">
         <f>SUM(T12:T18)</f>
-        <v>0</v>
+        <v>5581.708333333333</v>
       </c>
       <c r="U19" s="19">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>402.62812499999995</v>
       </c>
       <c r="V19" s="19">
-        <f t="shared" ref="V19" si="16">SUM(V12:V18)</f>
-        <v>0</v>
+        <f t="shared" ref="V19" si="24">SUM(V12:V18)</f>
+        <v>161.05125000000001</v>
       </c>
       <c r="W19" s="19">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>488.39947916666665</v>
       </c>
       <c r="X19" s="19">
-        <f t="shared" ref="X19" si="17">SUM(X12:X18)</f>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="58">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="58">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" ref="X19" si="25">SUM(X12:X18)</f>
+        <v>404.67385416666656</v>
+      </c>
+      <c r="Y19" s="56">
+        <f t="shared" si="22"/>
+        <v>6970.6498958333332</v>
+      </c>
+      <c r="Z19" s="56">
+        <f t="shared" si="22"/>
+        <v>1456.752708333333</v>
       </c>
       <c r="AD19" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+        <v>1786.5520833333335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
@@ -4128,114 +4507,114 @@
       <c r="K20" s="20"/>
       <c r="L20" s="20"/>
       <c r="M20" s="20">
-        <f t="shared" ref="M20:O20" si="18">+M11+M19</f>
-        <v>0</v>
+        <f t="shared" ref="M20:O20" si="26">+M11+M19</f>
+        <v>937.75</v>
       </c>
       <c r="N20" s="20">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="26"/>
+        <v>848.80208333333337</v>
       </c>
       <c r="O20" s="20">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="26"/>
+        <v>195.65625</v>
       </c>
       <c r="P20" s="20">
         <f>+P11+P19</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="65">
+        <v>1062</v>
+      </c>
+      <c r="Q20" s="62">
         <f>+Q11+Q19</f>
-        <v>0</v>
+        <v>4586.3333333333339</v>
       </c>
       <c r="R20" s="20">
         <f>+R11+R19</f>
-        <v>0</v>
+        <v>4586.3333333333339</v>
       </c>
       <c r="S20" s="20">
         <f>+S11+S19</f>
         <v>0</v>
       </c>
-      <c r="T20" s="47">
+      <c r="T20" s="46">
         <f>+T11+T19</f>
-        <v>0</v>
+        <v>10124.208333333332</v>
       </c>
       <c r="U20" s="20">
-        <f t="shared" ref="U20:Z20" si="19">+U11+U19</f>
-        <v>0</v>
+        <f t="shared" ref="U20:Z20" si="27">+U11+U19</f>
+        <v>666.44062499999995</v>
       </c>
       <c r="V20" s="20">
-        <f t="shared" ref="V20" si="20">+V11+V19</f>
-        <v>0</v>
+        <f t="shared" ref="V20" si="28">+V11+V19</f>
+        <v>266.57625000000002</v>
       </c>
       <c r="W20" s="20">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>885.86822916666665</v>
       </c>
       <c r="X20" s="20">
-        <f t="shared" ref="X20" si="21">+X11+X19</f>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="59">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="59">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f t="shared" ref="X20" si="29">+X11+X19</f>
+        <v>734.00510416666657</v>
+      </c>
+      <c r="Y20" s="57">
+        <f t="shared" si="27"/>
+        <v>13709.960312499999</v>
+      </c>
+      <c r="Z20" s="57">
+        <f t="shared" si="27"/>
+        <v>2552.8902083333332</v>
       </c>
       <c r="AD20" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+        <v>1786.5520833333335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="Z29" s="9"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="Z30" s="9"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
       <c r="Z31" s="9"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
     </row>
-    <row r="33" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
     </row>
-    <row r="34" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
     </row>
-    <row r="35" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
     </row>
-    <row r="36" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W36" s="16"/>
       <c r="X36" s="16"/>
     </row>
-    <row r="37" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W37" s="17"/>
       <c r="X37" s="17"/>
     </row>
-    <row r="38" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="21:24" x14ac:dyDescent="0.3">
       <c r="U38" s="17"/>
       <c r="V38" s="17"/>
     </row>
-    <row r="40" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W40" s="17"/>
       <c r="X40" s="17"/>
     </row>
-    <row r="41" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W41" s="18"/>
       <c r="X41" s="18"/>
     </row>
-    <row r="43" spans="21:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="21:24" x14ac:dyDescent="0.3">
       <c r="W43" s="17"/>
       <c r="X43" s="17"/>
     </row>
@@ -4254,6 +4633,9 @@
   <headerFooter>
     <oddFooter>&amp;L&amp;P de &amp;N</oddFooter>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="M11:Q11 S11:Z11" formula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4264,111 +4646,111 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="12" width="6.7109375" style="67" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="67"/>
+    <col min="1" max="12" width="6.6640625" style="64" customWidth="1"/>
+    <col min="13" max="16384" width="11.44140625" style="64"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="109"/>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="109"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-    </row>
-    <row r="3" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A3" s="127" t="s">
+    <row r="1" spans="1:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="107"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="107"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+    </row>
+    <row r="3" spans="1:12" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A3" s="136" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="63"/>
+      <c r="B4" s="122" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="63"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+    </row>
+    <row r="6" spans="1:12" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="134" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="128" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-    </row>
-    <row r="6" spans="1:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="125" t="s">
+      <c r="B6" s="134"/>
+      <c r="C6" s="134" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="125"/>
-      <c r="C6" s="125" t="s">
+      <c r="D6" s="134"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="134"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="134" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125"/>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="125"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125"/>
-      <c r="L6" s="73"/>
-    </row>
-    <row r="7" spans="1:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="134"/>
+      <c r="J6" s="134"/>
+      <c r="K6" s="134"/>
+      <c r="L6" s="70"/>
+    </row>
+    <row r="7" spans="1:12" ht="24.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="129" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B7" s="130"/>
       <c r="C7" s="131" t="str">
@@ -4380,383 +4762,437 @@
       <c r="F7" s="131"/>
       <c r="G7" s="131"/>
       <c r="H7" s="132" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I7" s="132"/>
       <c r="J7" s="132"/>
       <c r="K7" s="132"/>
-      <c r="L7" s="74"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="73"/>
-      <c r="L8" s="74"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="128" t="s">
+      <c r="L7" s="71"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="70"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="122" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="122"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="70">
+        <v>30</v>
+      </c>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
+    </row>
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="133" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="73">
-        <v>30</v>
-      </c>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="74"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="73"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="133" t="s">
-        <v>68</v>
       </c>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
       <c r="D11" s="133"/>
       <c r="E11" s="133"/>
       <c r="H11" s="133" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I11" s="133"/>
       <c r="J11" s="133"/>
       <c r="K11" s="133"/>
       <c r="L11" s="133"/>
     </row>
-    <row r="13" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="104" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="134">
+    <row r="13" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="102"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="123">
         <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$H$7:$H$18)</f>
         <v>450</v>
       </c>
-      <c r="E13" s="134"/>
-      <c r="H13" s="104" t="s">
+      <c r="E13" s="123"/>
+      <c r="H13" s="102" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="123">
+        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$V$7:$V$18)</f>
+        <v>23.371874999999999</v>
+      </c>
+      <c r="L13" s="123"/>
+    </row>
+    <row r="14" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="134">
-        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$V$7:$V$18)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="134"/>
-    </row>
-    <row r="14" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="104" t="s">
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="123">
+        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$AD$7:$AD$18)</f>
+        <v>188.4375</v>
+      </c>
+      <c r="E14" s="123"/>
+      <c r="H14" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="134">
-        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$AD$7:$AD$18)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="134"/>
-      <c r="H14" s="104" t="s">
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="123">
+        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$X$7:$X$18)</f>
+        <v>56.482031249999999</v>
+      </c>
+      <c r="L14" s="123"/>
+    </row>
+    <row r="15" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="123">
+        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$O$7:$O$18)</f>
+        <v>73.125</v>
+      </c>
+      <c r="E15" s="123"/>
+      <c r="H15" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="134">
-        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$X$7:$X$18)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="134"/>
-    </row>
-    <row r="15" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="104" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="134">
-        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$O$7:$O$18)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="134"/>
-      <c r="H15" s="104" t="s">
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="123">
+        <v>0</v>
+      </c>
+      <c r="L15" s="123"/>
+    </row>
+    <row r="16" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="104"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="134">
-        <v>0</v>
-      </c>
-      <c r="L15" s="134"/>
-    </row>
-    <row r="16" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="104" t="s">
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="123">
+        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$R$7:$R$18)</f>
+        <v>285</v>
+      </c>
+      <c r="E16" s="123"/>
+      <c r="H16" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="134">
-        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$R$7:$R$18)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="134"/>
-      <c r="H16" s="104" t="s">
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="123">
+        <v>0</v>
+      </c>
+      <c r="L16" s="123"/>
+    </row>
+    <row r="17" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="134">
-        <v>0</v>
-      </c>
-      <c r="L16" s="134"/>
-    </row>
-    <row r="17" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="104" t="s">
+      <c r="B17" s="102"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="123">
+        <v>0</v>
+      </c>
+      <c r="E17" s="123"/>
+      <c r="H17" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="104"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="134">
-        <v>0</v>
-      </c>
-      <c r="E17" s="134"/>
-      <c r="H17" s="135" t="s">
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="123">
+        <v>0</v>
+      </c>
+      <c r="L17" s="123"/>
+    </row>
+    <row r="18" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="134">
-        <v>0</v>
-      </c>
-      <c r="L17" s="134"/>
-    </row>
-    <row r="18" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="104" t="s">
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="123">
+        <v>0</v>
+      </c>
+      <c r="E18" s="123"/>
+      <c r="H18" s="128" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="134">
-        <v>0</v>
-      </c>
-      <c r="E18" s="134"/>
-      <c r="H18" s="135" t="s">
+      <c r="I18" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="135" t="s">
+      <c r="J18" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="123">
+        <v>0</v>
+      </c>
+      <c r="L18" s="123"/>
+    </row>
+    <row r="19" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="J18" s="135" t="s">
-        <v>81</v>
-      </c>
-      <c r="K18" s="134">
-        <v>0</v>
-      </c>
-      <c r="L18" s="134"/>
-    </row>
-    <row r="19" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="104" t="s">
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="123">
+        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$P$7:$P$18)</f>
+        <v>67.5</v>
+      </c>
+      <c r="E19" s="123"/>
+      <c r="H19" s="128" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="104"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="134">
-        <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$P$7:$P$18)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="134"/>
-      <c r="H19" s="135" t="s">
+      <c r="I19" s="128" t="s">
         <v>83</v>
       </c>
-      <c r="I19" s="135" t="s">
+      <c r="J19" s="128" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="123">
+        <v>0</v>
+      </c>
+      <c r="L19" s="123"/>
+    </row>
+    <row r="20" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="102" t="s">
         <v>84</v>
       </c>
-      <c r="J19" s="135" t="s">
-        <v>84</v>
-      </c>
-      <c r="K19" s="134">
-        <v>0</v>
-      </c>
-      <c r="L19" s="134"/>
-    </row>
-    <row r="20" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="104" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="134">
+      <c r="B20" s="102"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="123">
         <f>SUMIF(PLANILLA!$C$7:$C$18,$A$7,PLANILLA!$L$7:$L$18)</f>
         <v>30</v>
       </c>
-      <c r="E20" s="134"/>
-      <c r="H20" s="104" t="s">
+      <c r="E20" s="123"/>
+      <c r="H20" s="102" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="123">
+        <v>0</v>
+      </c>
+      <c r="L20" s="123"/>
+    </row>
+    <row r="21" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="134">
-        <v>0</v>
-      </c>
-      <c r="L20" s="134"/>
-    </row>
-    <row r="21" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="104" t="s">
+      <c r="B21" s="102"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="123">
+        <v>0</v>
+      </c>
+      <c r="E21" s="123"/>
+      <c r="H21" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="104"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="134">
-        <v>0</v>
-      </c>
-      <c r="E21" s="134"/>
-      <c r="H21" s="104" t="s">
+      <c r="I21" s="102"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="123">
+        <v>0</v>
+      </c>
+      <c r="L21" s="123"/>
+    </row>
+    <row r="22" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="102" t="s">
         <v>88</v>
       </c>
-      <c r="I21" s="104"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="134">
-        <v>0</v>
-      </c>
-      <c r="L21" s="134"/>
-    </row>
-    <row r="22" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="104" t="s">
+      <c r="B22" s="102"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="123">
+        <v>0</v>
+      </c>
+      <c r="E22" s="123"/>
+      <c r="H22" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="104"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="134">
-        <v>0</v>
-      </c>
-      <c r="E22" s="134"/>
-      <c r="H22" s="104" t="s">
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="123">
+        <v>0</v>
+      </c>
+      <c r="L22" s="123"/>
+    </row>
+    <row r="23" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="134">
-        <v>0</v>
-      </c>
-      <c r="L22" s="134"/>
-    </row>
-    <row r="23" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="104" t="s">
+      <c r="B23" s="102"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="123">
+        <v>0</v>
+      </c>
+      <c r="E23" s="123"/>
+      <c r="H23" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="104"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="134">
-        <v>0</v>
-      </c>
-      <c r="E23" s="134"/>
-      <c r="H23" s="104" t="s">
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="123">
+        <v>0</v>
+      </c>
+      <c r="L23" s="123"/>
+    </row>
+    <row r="24" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H24" s="124"/>
+      <c r="I24" s="124"/>
+      <c r="J24" s="124"/>
+    </row>
+    <row r="25" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="125" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="134">
-        <v>0</v>
-      </c>
-      <c r="L23" s="134"/>
-    </row>
-    <row r="24" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H24" s="136"/>
-      <c r="I24" s="136"/>
-      <c r="J24" s="136"/>
-    </row>
-    <row r="25" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="137" t="s">
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="126">
+        <f>SUM(D13:E23)</f>
+        <v>1094.0625</v>
+      </c>
+      <c r="E25" s="127"/>
+      <c r="H25" s="125" t="s">
         <v>93</v>
       </c>
-      <c r="B25" s="137"/>
-      <c r="C25" s="137"/>
-      <c r="D25" s="138">
-        <f>SUM(D13:E23)</f>
-        <v>480</v>
-      </c>
-      <c r="E25" s="139"/>
-      <c r="H25" s="137" t="s">
+      <c r="I25" s="125"/>
+      <c r="J25" s="125"/>
+      <c r="K25" s="126">
+        <f>SUM(K13:L23)</f>
+        <v>79.853906249999994</v>
+      </c>
+      <c r="L25" s="127"/>
+    </row>
+    <row r="26" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="124"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="124"/>
+    </row>
+    <row r="27" spans="1:12" s="72" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="I25" s="137"/>
-      <c r="J25" s="137"/>
-      <c r="K25" s="138">
-        <f>SUM(K13:L23)</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="139"/>
-    </row>
-    <row r="26" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
-    </row>
-    <row r="27" spans="1:12" s="75" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="137" t="s">
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="126">
+        <f>+D25-K25</f>
+        <v>1014.20859375</v>
+      </c>
+      <c r="E27" s="127"/>
+      <c r="G27" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="137"/>
-      <c r="C27" s="137"/>
-      <c r="D27" s="138">
-        <f>+D25-K25</f>
-        <v>480</v>
-      </c>
-      <c r="E27" s="139"/>
-      <c r="G27" s="101" t="s">
-        <v>96</v>
-      </c>
-      <c r="H27" s="101"/>
-      <c r="I27" s="101"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G28" s="128" t="str">
+      <c r="H27" s="99"/>
+      <c r="I27" s="99"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="99"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G28" s="122" t="str">
         <f>+IF(A7&lt;&gt;"",$C$7,"")</f>
         <v>Montacarguista</v>
       </c>
-      <c r="H28" s="128"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="128"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G29" s="128" t="s">
-        <v>97</v>
-      </c>
-      <c r="H29" s="128"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="128"/>
-      <c r="K29" s="128"/>
+      <c r="H28" s="122"/>
+      <c r="I28" s="122"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="122"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G29" s="122" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="122"/>
+      <c r="I29" s="122"/>
+      <c r="J29" s="122"/>
+      <c r="K29" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="H11:L11"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="K22:L22"/>
     <mergeCell ref="G29:K29"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="D23:E23"/>
@@ -4772,60 +5208,6 @@
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="G27:K27"/>
     <mergeCell ref="G28:K28"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="H11:L11"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="B4:L4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A8:XFD1048576 C7:XFD7 A1:XFD6" xr:uid="{CDFD469F-2D5D-4354-A9B8-7F419C6F5D60}">
